--- a/outputs/may_2026_financials_detail_20260609/2026年5月财务报表.xlsx
+++ b/outputs/may_2026_financials_detail_20260609/2026年5月财务报表.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10628"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4DAF7C4-4010-0F40-B0E1-A8ED76779ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B44E1D8-8552-8143-9D95-D7BBD76A1E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12240" yWindow="660" windowWidth="17160" windowHeight="17060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="92">
   <si>
     <t>支出来源</t>
   </si>
@@ -304,37 +304,7 @@
     <t>打赏邀请返现（陪玩）</t>
   </si>
   <si>
-    <t>3y</t>
-  </si>
-  <si>
-    <t>yoki</t>
-  </si>
-  <si>
-    <t>小霍</t>
-  </si>
-  <si>
-    <t>鸭鸭</t>
-  </si>
-  <si>
-    <t>iria</t>
-  </si>
-  <si>
-    <t>4月</t>
-  </si>
-  <si>
-    <t>5月</t>
-  </si>
-  <si>
-    <t>总金额</t>
-  </si>
-  <si>
     <t>公户收款手续费</t>
-  </si>
-  <si>
-    <t>kami</t>
-  </si>
-  <si>
-    <t>(Kami分红已经提前支付，727.67算作6月收入）</t>
   </si>
 </sst>
 </file>
@@ -453,7 +423,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -521,16 +491,13 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -882,15 +849,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
@@ -1798,13 +1765,13 @@
       <c r="A53" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C53" s="32" t="s">
-        <v>99</v>
-      </c>
-      <c r="D53" s="33">
+      <c r="C53" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="D53" s="19">
         <v>461.14</v>
       </c>
-      <c r="E53" s="34">
+      <c r="E53" s="32">
         <v>1</v>
       </c>
     </row>
@@ -1873,15 +1840,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="1"/>
@@ -2083,213 +2050,71 @@
         <v>73</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>96</v>
-      </c>
-      <c r="B24">
-        <v>14553.49</v>
-      </c>
-    </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>94</v>
-      </c>
-      <c r="B25" s="27">
-        <v>0.2</v>
-      </c>
-      <c r="C25">
-        <f>$B$24*B25</f>
-        <v>2910.6980000000003</v>
-      </c>
+      <c r="B25" s="27"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>91</v>
-      </c>
-      <c r="B26" s="27">
-        <v>0.18</v>
-      </c>
-      <c r="C26">
-        <f t="shared" ref="C26:C29" si="0">$B$24*B26</f>
-        <v>2619.6281999999997</v>
-      </c>
+      <c r="B26" s="27"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>92</v>
-      </c>
-      <c r="B27" s="27">
-        <v>0.42</v>
-      </c>
-      <c r="C27">
-        <f t="shared" si="0"/>
-        <v>6112.4657999999999</v>
-      </c>
+      <c r="B27" s="27"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>93</v>
-      </c>
-      <c r="B28" s="27">
-        <v>0.15</v>
-      </c>
-      <c r="C28">
-        <f>$B$24*B28</f>
-        <v>2183.0234999999998</v>
-      </c>
+      <c r="B28" s="27"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>95</v>
-      </c>
-      <c r="B29" s="27">
-        <v>0</v>
-      </c>
-      <c r="C29">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="B29" s="27"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>100</v>
-      </c>
-      <c r="B30" s="27">
-        <v>0.05</v>
-      </c>
-      <c r="C30" s="28">
-        <f>B24*B30</f>
-        <v>727.67450000000008</v>
-      </c>
-      <c r="D30" t="s">
-        <v>101</v>
-      </c>
+      <c r="B30" s="27"/>
+      <c r="C30" s="28"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>97</v>
-      </c>
-      <c r="B32" s="28">
-        <v>36875.980000000003</v>
-      </c>
+      <c r="B32" s="28"/>
       <c r="D32" s="28"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>94</v>
-      </c>
-      <c r="B33" s="27">
-        <v>0.2</v>
-      </c>
-      <c r="C33" s="28">
-        <f>$B$32*B33</f>
-        <v>7375.1960000000008</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>91</v>
-      </c>
-      <c r="B34" s="27">
-        <v>0.34</v>
-      </c>
-      <c r="C34" s="28">
-        <f t="shared" ref="C34:C37" si="1">$B$32*B34</f>
-        <v>12537.833200000003</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>92</v>
-      </c>
-      <c r="B35" s="27">
-        <v>0.38</v>
-      </c>
-      <c r="C35" s="28">
-        <f t="shared" si="1"/>
-        <v>14012.872400000002</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>93</v>
-      </c>
-      <c r="B36" s="27">
-        <v>0.04</v>
-      </c>
-      <c r="C36" s="28">
-        <f t="shared" si="1"/>
-        <v>1475.0392000000002</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>95</v>
-      </c>
-      <c r="B37" s="27">
-        <v>0.04</v>
-      </c>
-      <c r="C37" s="28">
-        <f t="shared" si="1"/>
-        <v>1475.0392000000002</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>98</v>
-      </c>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B33" s="27"/>
+      <c r="C33" s="28"/>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B34" s="27"/>
+      <c r="C34" s="28"/>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B35" s="27"/>
+      <c r="C35" s="28"/>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B36" s="27"/>
+      <c r="C36" s="28"/>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B37" s="27"/>
+      <c r="C37" s="28"/>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B39" s="27"/>
       <c r="C39" s="28"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>94</v>
-      </c>
-      <c r="C40" s="29">
-        <f>C25+C33</f>
-        <v>10285.894</v>
-      </c>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C40" s="29"/>
       <c r="D40" s="28"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>91</v>
-      </c>
-      <c r="C41" s="29">
-        <f>C26+C34</f>
-        <v>15157.461400000002</v>
-      </c>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C41" s="29"/>
       <c r="D41" s="28"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>92</v>
-      </c>
-      <c r="C42" s="29">
-        <f>C27+C35</f>
-        <v>20125.338200000002</v>
-      </c>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C42" s="29"/>
       <c r="D42" s="30"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>93</v>
-      </c>
-      <c r="C43" s="29">
-        <f>C28+C36</f>
-        <v>3658.0626999999999</v>
-      </c>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C43" s="29"/>
       <c r="D43" s="30"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>95</v>
-      </c>
-      <c r="C44" s="29">
-        <f t="shared" ref="C44" si="2">C29+C37</f>
-        <v>1475.0392000000002</v>
-      </c>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C44" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="1">
